--- a/UCAS mentee form.xlsx
+++ b/UCAS mentee form.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://imperiallondon-my.sharepoint.com/personal/hm1425_ic_ac_uk/Documents/STEMM/Term 1/UCAS mentoring testing/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://imperiallondon-my.sharepoint.com/personal/hm1425_ic_ac_uk/Documents/STEMM/Term 1/UCAS mentoring testing/Matching Algorithm/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13AFE710-26B6-44C8-8F84-35032937E573}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="24192" yWindow="2880" windowWidth="21600" windowHeight="11832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="33">
   <si>
     <t>ID</t>
   </si>
@@ -45,94 +45,85 @@
     <t>Last modified time</t>
   </si>
   <si>
-    <t>Faculty </t>
-  </si>
-  <si>
-    <t>Engineerings</t>
-  </si>
-  <si>
-    <t>Medicines</t>
-  </si>
-  <si>
-    <t>NatSci</t>
-  </si>
-  <si>
-    <t>Business </t>
-  </si>
-  <si>
-    <t>Okay with someone in Faculty but not desired course? </t>
+    <t>Name2</t>
+  </si>
+  <si>
+    <t>Email2</t>
+  </si>
+  <si>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>Course applying for</t>
   </si>
   <si>
     <t>anonymous</t>
   </si>
   <si>
-    <t>jj1</t>
-  </si>
-  <si>
-    <t>Engineering</t>
-  </si>
-  <si>
-    <t>mecheng </t>
-  </si>
-  <si>
-    <t>Yes</t>
+    <t>q</t>
   </si>
   <si>
     <t>q@q</t>
   </si>
   <si>
-    <t>eie</t>
+    <t>Brother</t>
+  </si>
+  <si>
+    <t>mecheng</t>
+  </si>
+  <si>
+    <t>w</t>
   </si>
   <si>
     <t>w@w</t>
   </si>
   <si>
-    <t>Medicine</t>
+    <t>Sister</t>
+  </si>
+  <si>
+    <t>medicine</t>
+  </si>
+  <si>
+    <t>e</t>
   </si>
   <si>
     <t>e@e</t>
   </si>
   <si>
-    <t>Physics</t>
-  </si>
-  <si>
-    <t>r@r</t>
-  </si>
-  <si>
-    <t>Business</t>
-  </si>
-  <si>
-    <t>Econimics </t>
+    <t>maths</t>
+  </si>
+  <si>
+    <t>r</t>
+  </si>
+  <si>
+    <t>r@R</t>
+  </si>
+  <si>
+    <t>chemistry</t>
+  </si>
+  <si>
+    <t>t</t>
   </si>
   <si>
     <t>t@t</t>
   </si>
   <si>
-    <t>No</t>
+    <t>y</t>
   </si>
   <si>
     <t>y@y</t>
   </si>
   <si>
+    <t>u</t>
+  </si>
+  <si>
     <t>u@u</t>
   </si>
   <si>
-    <t>Chemistry</t>
+    <t>i</t>
   </si>
   <si>
     <t>i@i</t>
-  </si>
-  <si>
-    <t>Maths</t>
-  </si>
-  <si>
-    <t>o@O</t>
-  </si>
-  <si>
-    <t>Finance </t>
-  </si>
-  <si>
-    <t>email2</t>
   </si>
 </sst>
 </file>
@@ -178,16 +169,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
+  <dxfs count="10">
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -232,22 +214,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:M11" totalsRowShown="0">
-  <autoFilter ref="A1:M11" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Start time" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Completion time" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Email" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Name" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Last modified time" dataDxfId="7"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="email2" dataDxfId="6"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Faculty " dataDxfId="5"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Engineerings" dataDxfId="4"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Medicines" dataDxfId="3"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="NatSci" dataDxfId="2"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Business " dataDxfId="1"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Okay with someone in Faculty but not desired course? " dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:J9" totalsRowShown="0">
+  <autoFilter ref="A1:J9" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Start time" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Completion time" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Email" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Name" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Last modified time" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Name2" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Email2" dataDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Gender" dataDxfId="1"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Course applying for" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -550,13 +529,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="13" width="20" bestFit="1" customWidth="1"/>
+    <col min="1" max="10" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -576,93 +555,84 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>46263.720104166663</v>
+        <v>46263.81726851852</v>
       </c>
       <c r="C2" s="1">
-        <v>46263.720381944448</v>
+        <v>46263.817442129628</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" t="s">
         <v>13</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>14</v>
       </c>
-      <c r="I2" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <v>46263.724733796298</v>
+        <v>46263.817453703705</v>
       </c>
       <c r="C3" s="1">
-        <v>46263.725069444445</v>
+        <v>46263.81753472222</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" t="s">
         <v>17</v>
       </c>
-      <c r="H3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>18</v>
       </c>
-      <c r="M3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" s="1">
-        <v>46263.725081018521</v>
+        <v>46263.817557870374</v>
       </c>
       <c r="C4" s="1">
-        <v>46263.725208333337</v>
+        <v>46263.817627314813</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" t="s">
@@ -671,200 +641,146 @@
       <c r="H4" t="s">
         <v>20</v>
       </c>
+      <c r="I4" t="s">
+        <v>13</v>
+      </c>
       <c r="J4" t="s">
-        <v>20</v>
-      </c>
-      <c r="M4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" s="1">
-        <v>46263.725219907406</v>
+        <v>46263.81763888889</v>
       </c>
       <c r="C5" s="1">
-        <v>46263.725324074076</v>
+        <v>46263.817708333336</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H5" t="s">
-        <v>9</v>
-      </c>
-      <c r="K5" t="s">
-        <v>22</v>
-      </c>
-      <c r="M5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="I5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" s="1">
-        <v>46263.725347222222</v>
+        <v>46263.817731481482</v>
       </c>
       <c r="C6" s="1">
-        <v>46263.725497685184</v>
+        <v>46263.817870370367</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H6" t="s">
-        <v>24</v>
-      </c>
-      <c r="L6" t="s">
-        <v>25</v>
-      </c>
-      <c r="M6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="I6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" s="1">
-        <v>46263.72550925926</v>
+        <v>46263.817893518521</v>
       </c>
       <c r="C7" s="1">
-        <v>46263.725601851853</v>
+        <v>46263.817986111113</v>
       </c>
       <c r="D7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H7" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="I7" t="s">
-        <v>15</v>
-      </c>
-      <c r="M7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="J7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" s="1">
-        <v>46263.725624999999</v>
+        <v>46263.818009259259</v>
       </c>
       <c r="C8" s="1">
-        <v>46263.725694444445</v>
+        <v>46263.818090277775</v>
       </c>
       <c r="D8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H8" t="s">
-        <v>20</v>
+        <v>30</v>
+      </c>
+      <c r="I8" t="s">
+        <v>17</v>
       </c>
       <c r="J8" t="s">
-        <v>20</v>
-      </c>
-      <c r="M8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" s="1">
-        <v>46263.725717592592</v>
+        <v>46263.818101851852</v>
       </c>
       <c r="C9" s="1">
-        <v>46263.725821759261</v>
+        <v>46263.818206018521</v>
       </c>
       <c r="D9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H9" t="s">
-        <v>9</v>
-      </c>
-      <c r="K9" t="s">
-        <v>30</v>
-      </c>
-      <c r="M9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" s="1">
-        <v>46263.72583333333</v>
-      </c>
-      <c r="C10" s="1">
-        <v>46263.725914351853</v>
-      </c>
-      <c r="D10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="1"/>
-      <c r="G10" t="s">
-        <v>31</v>
-      </c>
-      <c r="H10" t="s">
-        <v>9</v>
-      </c>
-      <c r="K10" t="s">
         <v>32</v>
       </c>
-      <c r="M10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1">
-        <v>46263.725925925923</v>
-      </c>
-      <c r="C11" s="1">
-        <v>46263.726041666669</v>
-      </c>
-      <c r="D11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="1"/>
-      <c r="G11" t="s">
-        <v>33</v>
-      </c>
-      <c r="H11" t="s">
+      <c r="I9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J9" t="s">
         <v>24</v>
-      </c>
-      <c r="L11" t="s">
-        <v>34</v>
-      </c>
-      <c r="M11" t="s">
-        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/UCAS mentee form.xlsx
+++ b/UCAS mentee form.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://imperiallondon-my.sharepoint.com/personal/hm1425_ic_ac_uk/Documents/STEMM/Term 1/UCAS mentoring testing/Matching Algorithm/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="49" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E9A2C03-167A-4F8A-9CDA-64CEEAFC140E}"/>
   <bookViews>
-    <workbookView xWindow="24192" yWindow="2880" windowWidth="21600" windowHeight="11832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="27000" windowHeight="14790" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="63">
   <si>
     <t>ID</t>
   </si>
@@ -124,6 +124,96 @@
   </si>
   <si>
     <t>i@i</t>
+  </si>
+  <si>
+    <t>o</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>d</t>
+  </si>
+  <si>
+    <t>f</t>
+  </si>
+  <si>
+    <t>g</t>
+  </si>
+  <si>
+    <t>o@o</t>
+  </si>
+  <si>
+    <t>p@o</t>
+  </si>
+  <si>
+    <t>a@a</t>
+  </si>
+  <si>
+    <t>s@s</t>
+  </si>
+  <si>
+    <t>d@d</t>
+  </si>
+  <si>
+    <t>f@f</t>
+  </si>
+  <si>
+    <t>g@g</t>
+  </si>
+  <si>
+    <t>h</t>
+  </si>
+  <si>
+    <t>j</t>
+  </si>
+  <si>
+    <t>k</t>
+  </si>
+  <si>
+    <t>l</t>
+  </si>
+  <si>
+    <t>z</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>v</t>
+  </si>
+  <si>
+    <t>h@h</t>
+  </si>
+  <si>
+    <t>j@j</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>b@b</t>
+  </si>
+  <si>
+    <t>n@n</t>
+  </si>
+  <si>
+    <t>m@m</t>
   </si>
 </sst>
 </file>
@@ -133,10 +223,18 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yy\ h:mm:ss"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -159,14 +257,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="10">
@@ -214,8 +316,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:J9" totalsRowShown="0">
-  <autoFilter ref="A1:J9" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:J29" totalsRowShown="0">
+  <autoFilter ref="A1:J29" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID" dataDxfId="9"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Start time" dataDxfId="8"/>
@@ -529,7 +631,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="10" width="20" bestFit="1" customWidth="1"/>
@@ -780,14 +882,519 @@
         <v>13</v>
       </c>
       <c r="J9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="2"/>
+      <c r="B10" s="1">
+        <v>46263.817453703705</v>
+      </c>
+      <c r="C10" s="1">
+        <v>46263.81753472222</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="2"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="2"/>
+      <c r="B11" s="1">
+        <v>46263.817557870374</v>
+      </c>
+      <c r="C11" s="1">
+        <v>46263.817627314813</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="2"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="2"/>
+      <c r="B12" s="1">
+        <v>46263.81726851852</v>
+      </c>
+      <c r="C12" s="1">
+        <v>46263.817442129628</v>
+      </c>
+      <c r="D12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="2"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="2"/>
+      <c r="B13" s="1">
+        <v>46263.817453703705</v>
+      </c>
+      <c r="C13" s="1">
+        <v>46263.81753472222</v>
+      </c>
+      <c r="D13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="2"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="2"/>
+      <c r="B14" s="1">
+        <v>46263.817557870374</v>
+      </c>
+      <c r="C14" s="1">
+        <v>46263.817627314813</v>
+      </c>
+      <c r="D14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="2"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="2"/>
+      <c r="B15" s="1">
+        <v>46263.81763888889</v>
+      </c>
+      <c r="C15" s="1">
+        <v>46263.817708333336</v>
+      </c>
+      <c r="D15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="2"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J15" s="2" t="s">
         <v>24</v>
       </c>
     </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="2"/>
+      <c r="B16" s="1">
+        <v>46263.817731481482</v>
+      </c>
+      <c r="C16" s="1">
+        <v>46263.817870370367</v>
+      </c>
+      <c r="D16" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" s="2"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="2"/>
+      <c r="B17" s="1">
+        <v>46263.817893518521</v>
+      </c>
+      <c r="C17" s="1">
+        <v>46263.817986111113</v>
+      </c>
+      <c r="D17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="2"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J17" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="2"/>
+      <c r="B18" s="1">
+        <v>46263.818009259259</v>
+      </c>
+      <c r="C18" s="1">
+        <v>46263.818090277775</v>
+      </c>
+      <c r="D18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" s="2"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="2"/>
+      <c r="B19" s="1">
+        <v>46263.818101851852</v>
+      </c>
+      <c r="C19" s="1">
+        <v>46263.818206018521</v>
+      </c>
+      <c r="D19" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19" s="2"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="2"/>
+      <c r="B20" s="1">
+        <v>46263.817453703705</v>
+      </c>
+      <c r="C20" s="1">
+        <v>46263.81753472222</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" s="2"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J20" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="2"/>
+      <c r="B21" s="1">
+        <v>46263.817557870374</v>
+      </c>
+      <c r="C21" s="1">
+        <v>46263.817627314813</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" s="2"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="2"/>
+      <c r="B22" s="1">
+        <v>46263.81763888889</v>
+      </c>
+      <c r="C22" s="1">
+        <v>46263.817708333336</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" s="2"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J22" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="2"/>
+      <c r="B23" s="1">
+        <v>46263.817731481482</v>
+      </c>
+      <c r="C23" s="1">
+        <v>46263.817870370367</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E23" s="2"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J23" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="2"/>
+      <c r="B24" s="1">
+        <v>46263.817893518521</v>
+      </c>
+      <c r="C24" s="1">
+        <v>46263.817986111113</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E24" s="2"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="2"/>
+      <c r="B25" s="1">
+        <v>46263.818009259259</v>
+      </c>
+      <c r="C25" s="1">
+        <v>46263.818090277775</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E25" s="2"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="2"/>
+      <c r="B26" s="1">
+        <v>46263.818101851852</v>
+      </c>
+      <c r="C26" s="1">
+        <v>46263.818206018521</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E26" s="2"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="2"/>
+      <c r="B27" s="1">
+        <v>46263.818101851852</v>
+      </c>
+      <c r="C27" s="1">
+        <v>46263.818206018521</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E27" s="2"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="2"/>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="2"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H10" r:id="rId1" xr:uid="{AAD28C64-5D5C-4946-94B0-D837798957EC}"/>
+    <hyperlink ref="H11" r:id="rId2" xr:uid="{FEF6941C-1EFE-47EF-BBC1-9D28B1F01D31}"/>
+    <hyperlink ref="H12" r:id="rId3" xr:uid="{D3429C98-3740-41A1-8505-529D888434F0}"/>
+    <hyperlink ref="H13" r:id="rId4" xr:uid="{0FFAC760-EFA7-444C-AE32-D0B5C5FFB304}"/>
+    <hyperlink ref="H14" r:id="rId5" xr:uid="{086005A6-49DC-4CD1-8BB5-B2CC70F2FE5F}"/>
+    <hyperlink ref="H15" r:id="rId6" xr:uid="{2F6B22FD-E58C-4AD8-BCE1-65E739CB0D0D}"/>
+    <hyperlink ref="H16" r:id="rId7" xr:uid="{CDEEF360-BF94-426D-8103-1B50E6B4B774}"/>
+    <hyperlink ref="H17" r:id="rId8" xr:uid="{29C4689A-61F8-4B04-B615-24520629861F}"/>
+    <hyperlink ref="H18" r:id="rId9" xr:uid="{F799AD27-EC40-4F45-8186-1BFC235A144C}"/>
+    <hyperlink ref="H19:H24" r:id="rId10" display="j@j" xr:uid="{C8C26D3B-AB1F-433D-AAEF-6F3AE909D584}"/>
+    <hyperlink ref="H25" r:id="rId11" xr:uid="{285C02A1-B33E-46C5-99CC-BE453B278E4F}"/>
+    <hyperlink ref="H26" r:id="rId12" xr:uid="{CABDF7B6-C784-4163-9B03-219D7975B26F}"/>
+    <hyperlink ref="H27" r:id="rId13" xr:uid="{B1038DBB-E952-4FB7-8C7E-5E6D678C4DFA}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId14"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId15"/>
   </tableParts>
 </worksheet>
 </file>